--- a/src/nodes/P/compressor_stage_1_blade_stator_coordinates_foil.xlsx
+++ b/src/nodes/P/compressor_stage_1_blade_stator_coordinates_foil.xlsx
@@ -349,7 +349,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0</v>
+        <v>0.00016085087928332452</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -357,7 +357,7 @@
         <v>0.002978719986728232</v>
       </c>
       <c r="B2">
-        <v>0.0010567664553726773</v>
+        <v>0.0007202488875408436</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.005957439973456464</v>
       </c>
       <c r="B3">
-        <v>0.0016818579151478383</v>
+        <v>0.0012421988451067516</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0089361599601846965</v>
       </c>
       <c r="B4">
-        <v>0.0022291991884417356</v>
+        <v>0.0017337594975228648</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.011914879946912928</v>
       </c>
       <c r="B5">
-        <v>0.0027184996360296743</v>
+        <v>0.002201989590330999</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.01489359993364116</v>
       </c>
       <c r="B6">
-        <v>0.0031578155219520827</v>
+        <v>0.0026509586979187407</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.017872319920369393</v>
       </c>
       <c r="B7">
-        <v>0.0035517578839226543</v>
+        <v>0.003072779710056755</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.020851039907097624</v>
       </c>
       <c r="B8">
-        <v>0.0039030500946648674</v>
+        <v>0.003459144066057203</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.023829759893825856</v>
       </c>
       <c r="B9">
-        <v>0.0042159285182155077</v>
+        <v>0.0038120140880151588</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.026808479880554088</v>
       </c>
       <c r="B10">
-        <v>0.0044949631470491544</v>
+        <v>0.0041351936959786373</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.029787199867282319</v>
       </c>
       <c r="B11">
-        <v>0.0047445454960782611</v>
+        <v>0.0044295823190244974</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.032765919854010554</v>
       </c>
       <c r="B12">
-        <v>0.0049670296846610713</v>
+        <v>0.0046953532634868133</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.035744639840738786</v>
       </c>
       <c r="B13">
-        <v>0.0051567987275010895</v>
+        <v>0.0049326798356996576</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.038723359827467017</v>
       </c>
       <c r="B14">
-        <v>0.0053104997115312183</v>
+        <v>0.0051417432194543079</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.041702079814195249</v>
       </c>
       <c r="B15">
-        <v>0.0054418071172566808</v>
+        <v>0.0053227561083708666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.044680799800923481</v>
       </c>
       <c r="B16">
-        <v>0.0055632630896164624</v>
+        <v>0.0054759390735266405</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.047659519787651712</v>
       </c>
       <c r="B17">
-        <v>0.0056658530377122684</v>
+        <v>0.0056015126859989385</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.050638239774379951</v>
       </c>
       <c r="B18">
-        <v>0.005737930811931794</v>
+        <v>0.0056996131022397168</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.053616959761108175</v>
       </c>
       <c r="B19">
-        <v>0.0057788807636439746</v>
+        <v>0.0057700388201995367</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.056595679747836414</v>
       </c>
       <c r="B20">
-        <v>0.0057908448694630587</v>
+        <v>0.0058125039232036074</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.059574399734564638</v>
       </c>
       <c r="B21">
-        <v>0.0057759651060032904</v>
+        <v>0.00582672249457714</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.062553119721292877</v>
       </c>
       <c r="B22">
-        <v>0.0057360014351248581</v>
+        <v>0.0058125039232036074</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.065531839708021108</v>
       </c>
       <c r="B23">
-        <v>0.005671185759671721</v>
+        <v>0.0057700388201995367</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.06851055969474934</v>
       </c>
       <c r="B24">
-        <v>0.0055813679677337831</v>
+        <v>0.0056996131022397168</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.071489279681477572</v>
       </c>
       <c r="B25">
-        <v>0.0054663979474009446</v>
+        <v>0.0056015126859989377</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.0744679996682058</v>
       </c>
       <c r="B26">
-        <v>0.0053260613165100534</v>
+        <v>0.0054759390735266405</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.077446719654934035</v>
       </c>
       <c r="B27">
-        <v>0.0051598866118857285</v>
+        <v>0.0053227561083708658</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.080425439641662266</v>
       </c>
       <c r="B28">
-        <v>0.0049673381000995345</v>
+        <v>0.005141743219454307</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.0834041596283905</v>
       </c>
       <c r="B29">
-        <v>0.0047478800477230359</v>
+        <v>0.0049326798356996559</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.086382879615118729</v>
       </c>
       <c r="B30">
-        <v>0.0045012584694086987</v>
+        <v>0.0046953532634868124</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.089361599601846961</v>
       </c>
       <c r="B31">
-        <v>0.0042283463721325939</v>
+        <v>0.0044295823190244974</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.092340319588575193</v>
       </c>
       <c r="B32">
-        <v>0.0039302985109516859</v>
+        <v>0.0041351936959786373</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.095319039575303424</v>
       </c>
       <c r="B33">
-        <v>0.0036082696409229483</v>
+        <v>0.0038120140880151588</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.098297759562031656</v>
       </c>
       <c r="B34">
-        <v>0.0032629549015757253</v>
+        <v>0.0034591440660572017</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.1012764795487599</v>
       </c>
       <c r="B35">
-        <v>0.0028932109703288674</v>
+        <v>0.0030727797100567529</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.10425519953548812</v>
       </c>
       <c r="B36">
-        <v>0.0024974349090736031</v>
+        <v>0.0026509586979187407</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.10723391952221635</v>
       </c>
       <c r="B37">
-        <v>0.0020740237797011543</v>
+        <v>0.002201989590330999</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.11021263950894458</v>
       </c>
       <c r="B38">
-        <v>0.0016202501156829987</v>
+        <v>0.0017337594975228637</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.11319135949567283</v>
       </c>
       <c r="B39">
-        <v>0.0011288883368116075</v>
+        <v>0.0012421988451067495</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.11617007948240106</v>
       </c>
       <c r="B40">
-        <v>0.00059158833445970016</v>
+        <v>0.00072024888754084067</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -669,7 +669,7 @@
         <v>0.11914879946912928</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>0.0001608508792833246</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.11914879946912928</v>
       </c>
       <c r="B42">
-        <v>5.1672554893387872E-20</v>
+        <v>-0.00016085087928332443</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.11617007948240106</v>
       </c>
       <c r="B43">
-        <v>0.00019939122060373717</v>
+        <v>7.0729878904683387E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.11319135949567283</v>
       </c>
       <c r="B44">
-        <v>0.00041185086160638873</v>
+        <v>0.00029854035331124682</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.11021263950894458</v>
       </c>
       <c r="B45">
-        <v>0.0006291296677023734</v>
+        <v>0.00051562107448042179</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.10723391952221635</v>
       </c>
       <c r="B46">
-        <v>0.00084297838358611055</v>
+        <v>0.00071501257295626566</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.10425519953548812</v>
       </c>
       <c r="B47">
-        <v>0.0010462686591256737</v>
+        <v>0.00089274187916219764</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.1012764795487599</v>
       </c>
       <c r="B48">
-        <v>0.0012363557648837524</v>
+        <v>0.0010567820230390861</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.098297759562031656</v>
       </c>
       <c r="B49">
-        <v>0.0014117158765966924</v>
+        <v>0.0012155235068849093</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.095319039575303424</v>
       </c>
       <c r="B50">
-        <v>0.0015708251700008375</v>
+        <v>0.0013670807229086265</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.092340319588575193</v>
       </c>
       <c r="B51">
-        <v>0.0017126154914906002</v>
+        <v>0.0015077219515294371</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.089361599601846961</v>
       </c>
       <c r="B52">
-        <v>0.0018378413700926679</v>
+        <v>0.0016366071360965127</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.086382879615118729</v>
       </c>
       <c r="B53">
-        <v>0.0019477130054917956</v>
+        <v>0.0017536191356915187</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.0834041596283905</v>
       </c>
       <c r="B54">
-        <v>0.0020434405973727408</v>
+        <v>0.001858640809396121</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.080425439641662266</v>
       </c>
       <c r="B55">
-        <v>0.0021259488707411939</v>
+        <v>0.0019515432659546078</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.077446719654934035</v>
       </c>
       <c r="B56">
-        <v>0.0021950206518865927</v>
+        <v>0.0020321506127617644</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.0744679996682058</v>
       </c>
       <c r="B57">
-        <v>0.0022501532924193075</v>
+        <v>0.0021002752068749989</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.071489279681477572</v>
       </c>
       <c r="B58">
-        <v>0.0022908441439497126</v>
+        <v>0.0021557294053517191</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.06851055969474934</v>
       </c>
       <c r="B59">
-        <v>0.0023166511706947637</v>
+        <v>0.0021984063328502976</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.065531839708021108</v>
       </c>
       <c r="B60">
-        <v>0.0023273747872977596</v>
+        <v>0.0022285221844329569</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.062553119721292877</v>
       </c>
       <c r="B61">
-        <v>0.0023228760210085814</v>
+        <v>0.0022463739227628833</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.059574399734564638</v>
       </c>
       <c r="B62">
-        <v>0.0023030158990771108</v>
+        <v>0.0022522585105032617</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.056595679747836414</v>
       </c>
       <c r="B63">
-        <v>0.0022680336777174872</v>
+        <v>0.0022463739227628833</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.053616959761108175</v>
       </c>
       <c r="B64">
-        <v>0.0022196815290008768</v>
+        <v>0.0022285221844329569</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.050638239774379951</v>
       </c>
       <c r="B65">
-        <v>0.0021600898539627035</v>
+        <v>0.0021984063328502976</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.047659519787651712</v>
       </c>
       <c r="B66">
-        <v>0.0020913890536383897</v>
+        <v>0.0021557294053517195</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.044680799800923481</v>
       </c>
       <c r="B67">
-        <v>0.0020129488529265984</v>
+        <v>0.0021002752068749989</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.041702079814195249</v>
       </c>
       <c r="B68">
-        <v>0.0019130962721789484</v>
+        <v>0.0020321506127617649</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.038723359827467017</v>
       </c>
       <c r="B69">
-        <v>0.0017827854768801945</v>
+        <v>0.0019515432659546086</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.035744639840738786</v>
       </c>
       <c r="B70">
-        <v>0.0016345219175946898</v>
+        <v>0.0018586408093961217</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.032765919854010554</v>
       </c>
       <c r="B71">
-        <v>0.00148194001497277</v>
+        <v>0.0017536191356915193</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.029787199867282319</v>
       </c>
       <c r="B72">
-        <v>0.0013216387849291154</v>
+        <v>0.0016366071360965127</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.026808479880554088</v>
       </c>
       <c r="B73">
-        <v>0.0011479493035955681</v>
+        <v>0.0015077219515294369</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.023829759893825856</v>
       </c>
       <c r="B74">
-        <v>0.00096316629270827808</v>
+        <v>0.0013670807229086265</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.020851039907097624</v>
       </c>
       <c r="B75">
-        <v>0.00077161808969844839</v>
+        <v>0.0012155235068849095</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.017872319920369393</v>
       </c>
       <c r="B76">
-        <v>0.00057780384917318738</v>
+        <v>0.001056782023039087</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.01489359993364116</v>
       </c>
       <c r="B77">
-        <v>0.00038588515954318979</v>
+        <v>0.00089274187916219764</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.011914879946912928</v>
       </c>
       <c r="B78">
-        <v>0.00019850252725759054</v>
+        <v>0.00071501257295626566</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0089361599601846965</v>
       </c>
       <c r="B79">
-        <v>2.0180446284078394E-05</v>
+        <v>0.00051562107448042233</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.005957439973456464</v>
       </c>
       <c r="B80">
-        <v>-0.000141118716729839</v>
+        <v>0.0002985403533112478</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.002978719986728232</v>
       </c>
       <c r="B81">
-        <v>-0.00026578521873465766</v>
+        <v>7.07298789046847E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>-0.00016085087928332452</v>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +1023,7 @@
         <v>0.0033324055681336548</v>
       </c>
       <c r="B2">
-        <v>0.0015814650228816853</v>
+        <v>0.0018280630349235758</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.00666481113626731</v>
       </c>
       <c r="B3">
-        <v>0.0023784257580487878</v>
+        <v>0.00271833112599842</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0099972167044009661</v>
       </c>
       <c r="B4">
-        <v>0.0030507272650749889</v>
+        <v>0.0034626125932963082</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.013329622272534619</v>
       </c>
       <c r="B5">
-        <v>0.0036350531376490216</v>
+        <v>0.0041049223227558667</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.016662027840668274</v>
       </c>
       <c r="B6">
-        <v>0.0041463628547334522</v>
+        <v>0.0046632065669838319</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.019994433408801932</v>
       </c>
       <c r="B7">
-        <v>0.0045931969458470308</v>
+        <v>0.0051477092323844714</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.023326838976935587</v>
       </c>
       <c r="B8">
-        <v>0.00498057871279486</v>
+        <v>0.0055644537495039359</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.026659244545069238</v>
       </c>
       <c r="B9">
-        <v>0.0053163578895299391</v>
+        <v>0.0059228557029302646</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.029991650113202893</v>
       </c>
       <c r="B10">
-        <v>0.0056090088886906354</v>
+        <v>0.0062330805043645018</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.033324055681336548</v>
       </c>
       <c r="B11">
-        <v>0.0058666784055089044</v>
+        <v>0.0065049007199178615</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.0366564612494702</v>
       </c>
       <c r="B12">
-        <v>0.0060937167808283082</v>
+        <v>0.0067435334958636075</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.039988866817603864</v>
       </c>
       <c r="B13">
-        <v>0.0062796166553452382</v>
+        <v>0.0069363671447130182</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.043321272385737512</v>
       </c>
       <c r="B14">
-        <v>0.0064180947227669306</v>
+        <v>0.00707585905390657</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.046653677953871174</v>
       </c>
       <c r="B15">
-        <v>0.00653462158899117</v>
+        <v>0.007192571744363478</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.049986083522004822</v>
       </c>
       <c r="B16">
-        <v>0.0066525587647546193</v>
+        <v>0.0073145370072929816</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.053318489090138477</v>
       </c>
       <c r="B17">
-        <v>0.0067550774679589112</v>
+        <v>0.0074215585815856416</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.056650894658272138</v>
       </c>
       <c r="B18">
-        <v>0.0068204451111238467</v>
+        <v>0.0074875558826048459</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.059983300226405786</v>
       </c>
       <c r="B19">
-        <v>0.0068475041780769394</v>
+        <v>0.0075111390839239338</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.063315705794539448</v>
       </c>
       <c r="B20">
-        <v>0.0068402409204726287</v>
+        <v>0.0074970910486687366</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.0666481113626731</v>
       </c>
       <c r="B21">
-        <v>0.0068026415899653534</v>
+        <v>0.0074501946399650847</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.069980516930806758</v>
       </c>
       <c r="B22">
-        <v>0.006737982632499551</v>
+        <v>0.007374381163043787</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.0733129224989404</v>
       </c>
       <c r="B23">
-        <v>0.0066467012711796435</v>
+        <v>0.0072701756915555674</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.076645328067074067</v>
       </c>
       <c r="B24">
-        <v>0.0065285249234000508</v>
+        <v>0.007137251741256131</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.079977733635207729</v>
       </c>
       <c r="B25">
-        <v>0.0063831810065551947</v>
+        <v>0.006975282827901181</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.083310139203341377</v>
       </c>
       <c r="B26">
-        <v>0.006210279504679255</v>
+        <v>0.0067838017486977651</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.086642544771475025</v>
       </c>
       <c r="B27">
-        <v>0.0060089606683654592</v>
+        <v>0.0065617784266582971</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.089974950339608686</v>
       </c>
       <c r="B28">
-        <v>0.0057782473148467964</v>
+        <v>0.0063080420662465367</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.093307355907742348</v>
       </c>
       <c r="B29">
-        <v>0.0055171622613562569</v>
+        <v>0.0060214218719262412</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.096639761475876</v>
       </c>
       <c r="B30">
-        <v>0.0052252561158147876</v>
+        <v>0.0057013806010720565</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.099972167044009644</v>
       </c>
       <c r="B31">
-        <v>0.0049041906488951756</v>
+        <v>0.0053499152227021868</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.10330457261214331</v>
       </c>
       <c r="B32">
-        <v>0.0045561554219581638</v>
+        <v>0.0049696562587457161</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.10663697818027695</v>
       </c>
       <c r="B33">
-        <v>0.0041833399963644956</v>
+        <v>0.0045632342311317329</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.10996938374841062</v>
       </c>
       <c r="B34">
-        <v>0.0037870795608990087</v>
+        <v>0.00413225462839293</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.11330178931654428</v>
       </c>
       <c r="B35">
-        <v>0.003365291814042905</v>
+        <v>0.0036742228054764121</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.11663419488467791</v>
       </c>
       <c r="B36">
-        <v>0.0029150400817014805</v>
+        <v>0.0031856190839328917</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.11996660045281157</v>
       </c>
       <c r="B37">
-        <v>0.002433387689780026</v>
+        <v>0.0026629237853130721</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.12329900602094523</v>
       </c>
       <c r="B38">
-        <v>0.0019153036197400903</v>
+        <v>0.0021001042116194626</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.1266314115890789</v>
       </c>
       <c r="B39">
-        <v>0.0013473794752682327</v>
+        <v>0.0014810755866617542</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.12996381715721256</v>
       </c>
       <c r="B40">
-        <v>0.00071411251560726406</v>
+        <v>0.0007872401147014361</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.13329622272534619</v>
       </c>
       <c r="B42">
-        <v>-9.0325033914332512E-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.12996381715721256</v>
       </c>
       <c r="B43">
-        <v>-1.7163475334457963E-05</v>
+        <v>-9.02910744286301E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.1266314115890789</v>
       </c>
       <c r="B44">
-        <v>1.0418361333012647E-05</v>
+        <v>-0.00012327775006050929</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.12329900602094523</v>
       </c>
       <c r="B45">
-        <v>6.7297700946368158E-05</v>
+        <v>-0.00011750289093300401</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.11996660045281157</v>
       </c>
       <c r="B46">
-        <v>0.00013802673444956472</v>
+        <v>-9.150936108348136E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.11663419488467791</v>
       </c>
       <c r="B47">
-        <v>0.00020925005938737481</v>
+        <v>-6.1328942844035707E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.11330178931654428</v>
       </c>
       <c r="B48">
-        <v>0.00027598189970783592</v>
+        <v>-3.2949091725670888E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.10996938374841062</v>
       </c>
       <c r="B49">
-        <v>0.00033532888595980267</v>
+        <v>-9.8461815341177012E-06</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.10663697818027695</v>
       </c>
       <c r="B50">
-        <v>0.00038439764869212906</v>
+        <v>4.5034139248926262E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.10330457261214331</v>
       </c>
       <c r="B51">
-        <v>0.00042114705408264247</v>
+        <v>7.6462172950906354E-06</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.099972167044009644</v>
       </c>
       <c r="B52">
-        <v>0.00044694491082506414</v>
+        <v>1.2203370180532689E-06</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.096639761475876</v>
       </c>
       <c r="B53">
-        <v>0.00046401126324208868</v>
+        <v>-1.2113222015180868E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.093307355907742348</v>
       </c>
       <c r="B54">
-        <v>0.00047456615565641093</v>
+        <v>-2.9693454913573345E-05</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.089974950339608686</v>
       </c>
       <c r="B55">
-        <v>0.00048029980084939326</v>
+        <v>-4.9494950550346724E-05</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.086642544771475025</v>
       </c>
       <c r="B56">
-        <v>0.00048078308543707021</v>
+        <v>-7.2034672855768371E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.083310139203341377</v>
       </c>
       <c r="B57">
-        <v>0.0004750570644941441</v>
+        <v>-9.8465179524366727E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.079977733635207729</v>
       </c>
       <c r="B58">
-        <v>0.0004621627930953173</v>
+        <v>-0.00012993902825067015</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.076645328067074067</v>
       </c>
       <c r="B59">
-        <v>0.000441256744839245</v>
+        <v>-0.00016747007301683541</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.0733129224989404</v>
       </c>
       <c r="B60">
-        <v>0.0004119570674203941</v>
+        <v>-0.00021151735295553059</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.069980516930806758</v>
       </c>
       <c r="B61">
-        <v>0.00037399732705718444</v>
+        <v>-0.00026240120348705186</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.0666481113626731</v>
       </c>
       <c r="B62">
-        <v>0.00032711108996803589</v>
+        <v>-0.00032044196003169561</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.063315705794539448</v>
       </c>
       <c r="B63">
-        <v>0.00027173963851154253</v>
+        <v>-0.00038511048968456582</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.059983300226405786</v>
       </c>
       <c r="B64">
-        <v>0.0002111551196069954</v>
+        <v>-0.00045247978623999888</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.056650894658272138</v>
       </c>
       <c r="B65">
-        <v>0.00014933739631385994</v>
+        <v>-0.00051777337516713858</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.053318489090138477</v>
       </c>
       <c r="B66">
-        <v>9.0266331691601234E-05</v>
+        <v>-0.00057621478193512941</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.049986083522004822</v>
       </c>
       <c r="B67">
-        <v>3.2776339370997808E-05</v>
+        <v>-0.00062920190316736373</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.046653677953871174</v>
       </c>
       <c r="B68">
-        <v>-4.4879964731919684E-05</v>
+        <v>-0.000702830120104228</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.043321272385737512</v>
       </c>
       <c r="B69">
-        <v>-0.00015954858862946377</v>
+        <v>-0.00081731291976910262</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.039988866817603864</v>
       </c>
       <c r="B70">
-        <v>-0.00028788823833256888</v>
+        <v>-0.00094463872770034923</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.0366564612494702</v>
       </c>
       <c r="B71">
-        <v>-0.00040445036952468173</v>
+        <v>-0.0010542670845599803</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.033324055681336548</v>
       </c>
       <c r="B72">
-        <v>-0.00051554473858067128</v>
+        <v>-0.0011537670529896285</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.029991650113202893</v>
       </c>
       <c r="B73">
-        <v>-0.00063170726804802921</v>
+        <v>-0.0012557788837218953</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.026659244545069238</v>
       </c>
       <c r="B74">
-        <v>-0.00074862024447331363</v>
+        <v>-0.0013551180578736386</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.023326838976935587</v>
       </c>
       <c r="B75">
-        <v>-0.00085817165429590036</v>
+        <v>-0.0014420466910049765</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.019994433408801932</v>
       </c>
       <c r="B76">
-        <v>-0.00095192591952737065</v>
+        <v>-0.001506438206064811</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.016662027840668274</v>
       </c>
       <c r="B77">
-        <v>-0.0010220742677703495</v>
+        <v>-0.0015389179800207296</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.013329622272534619</v>
       </c>
       <c r="B78">
-        <v>-0.001063638713419431</v>
+        <v>-0.0015335078985262759</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0099972167044009661</v>
       </c>
       <c r="B79">
-        <v>-0.0010681260171382088</v>
+        <v>-0.0014800113453595281</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.00666481113626731</v>
       </c>
       <c r="B80">
-        <v>-0.0010206279214475397</v>
+        <v>-0.0013605332893971722</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0033324055681336548</v>
       </c>
       <c r="B81">
-        <v>-0.00088451509753721908</v>
+        <v>-0.0011311131095791095</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0035744639840738779</v>
       </c>
       <c r="B2">
-        <v>0.0021892904413831956</v>
+        <v>0.002718311111026129</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0071489279681477558</v>
       </c>
       <c r="B3">
-        <v>0.0032101417877832971</v>
+        <v>0.0039393324405343679</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.010723391952221635</v>
       </c>
       <c r="B4">
-        <v>0.004053418171872018</v>
+        <v>0.0049370256687350806</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.014297855936295512</v>
       </c>
       <c r="B5">
-        <v>0.0047741877820872353</v>
+        <v>0.0057821866255960679</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.017872319920369389</v>
       </c>
       <c r="B6">
-        <v>0.005394896950498944</v>
+        <v>0.0065036690954625009</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.021446783904443271</v>
       </c>
       <c r="B7">
-        <v>0.0059283541259756746</v>
+        <v>0.00711793573987546</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.025021247888517149</v>
       </c>
       <c r="B8">
-        <v>0.0063820866673430848</v>
+        <v>0.0076346594693296518</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.028595711872591023</v>
       </c>
       <c r="B9">
-        <v>0.0067678679215582406</v>
+        <v>0.0080689728117611312</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0321701758566649</v>
       </c>
       <c r="B10">
-        <v>0.0070984100697882189</v>
+        <v>0.0084372156071696527</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.035744639840738779</v>
       </c>
       <c r="B11">
-        <v>0.00738593464190876</v>
+        <v>0.0087550973263684165</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.039319103824812657</v>
       </c>
       <c r="B12">
-        <v>0.0076369629408689866</v>
+        <v>0.0090309988087443078</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.042893567808886542</v>
       </c>
       <c r="B13">
-        <v>0.0078357060132028845</v>
+        <v>0.0092446167371654439</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.046468031792960413</v>
       </c>
       <c r="B14">
-        <v>0.0079727188864826444</v>
+        <v>0.0093838045803430539</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.0500424957770343</v>
       </c>
       <c r="B15">
-        <v>0.0080862427688484159</v>
+        <v>0.0094977271068795079</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.053616959761108168</v>
       </c>
       <c r="B16">
-        <v>0.00821135231015499</v>
+        <v>0.0096314780048309349</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.057191423745182046</v>
       </c>
       <c r="B17">
-        <v>0.0083227697465477844</v>
+        <v>0.0097525553401773338</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.060765887729255931</v>
       </c>
       <c r="B18">
-        <v>0.00838785416582166</v>
+        <v>0.0098189905490092943</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.0643403517133298</v>
       </c>
       <c r="B19">
-        <v>0.0084048644760786329</v>
+        <v>0.00982854416993587</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.06791481569740368</v>
       </c>
       <c r="B20">
-        <v>0.00837978454049751</v>
+        <v>0.009788909017195738</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.071489279681477558</v>
       </c>
       <c r="B21">
-        <v>0.0083185982222570946</v>
+        <v>0.0097077779050275658</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.075063743665551436</v>
       </c>
       <c r="B22">
-        <v>0.008226224214339278</v>
+        <v>0.0095914743799857885</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.078638207649625314</v>
       </c>
       <c r="B23">
-        <v>0.00810332052893829</v>
+        <v>0.0094408449178878754</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.0822126716336992</v>
       </c>
       <c r="B24">
-        <v>0.007949480008051452</v>
+        <v>0.00925536672686706</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.085787135617773083</v>
       </c>
       <c r="B25">
-        <v>0.0077642954936760792</v>
+        <v>0.0090345170150565712</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.089361599601846947</v>
       </c>
       <c r="B26">
-        <v>0.00754718419294369</v>
+        <v>0.0087775474025799886</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.092936063585920825</v>
       </c>
       <c r="B27">
-        <v>0.0072968607735225937</v>
+        <v>0.0084828071575222489</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.0965105275699947</v>
       </c>
       <c r="B28">
-        <v>0.0070118642682153072</v>
+        <v>0.0081484199599586426</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.1000849915540686</v>
       </c>
       <c r="B29">
-        <v>0.006690733709824339</v>
+        <v>0.0077725094899644565</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.10365945553814247</v>
       </c>
       <c r="B30">
-        <v>0.0063328014352719711</v>
+        <v>0.0073542196208387324</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.10723391952221634</v>
       </c>
       <c r="B31">
-        <v>0.0059405729979595577</v>
+        <v>0.0068967749987755289</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.11080838350629021</v>
       </c>
       <c r="B32">
-        <v>0.0055173472554082195</v>
+        <v>0.0064044204631926536</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.11438284749036409</v>
       </c>
       <c r="B33">
-        <v>0.0050664230651390743</v>
+        <v>0.005881400853507919</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.11795731147443798</v>
       </c>
       <c r="B34">
-        <v>0.0045898170410335675</v>
+        <v>0.00533031265102518</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.12153177545851186</v>
       </c>
       <c r="B35">
-        <v>0.00408441682241442</v>
+        <v>0.0047471589045924656</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.12510623944258573</v>
       </c>
       <c r="B36">
-        <v>0.0035458278049646783</v>
+        <v>0.0041262943049438488</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.1286807034266596</v>
       </c>
       <c r="B37">
-        <v>0.00296965538436738</v>
+        <v>0.0034620735428133962</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.13225516741073348</v>
       </c>
       <c r="B38">
-        <v>0.0023483605878030149</v>
+        <v>0.0027448087669952647</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.13582963139480736</v>
       </c>
       <c r="B39">
-        <v>0.0016618269684418533</v>
+        <v>0.0019486419585239409</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.13940409537888124</v>
       </c>
       <c r="B40">
-        <v>0.00088679371095160876</v>
+        <v>0.0010436725564939944</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.13940409537888124</v>
       </c>
       <c r="B43">
-        <v>-0.00021135820784508755</v>
+        <v>-0.00036823705338747293</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.13582963139480736</v>
       </c>
       <c r="B44">
-        <v>-0.00034587796213275874</v>
+        <v>-0.00063269295221484616</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.13225516741073348</v>
       </c>
       <c r="B45">
-        <v>-0.0004267766665427359</v>
+        <v>-0.00082322484573498585</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.1286807034266596</v>
       </c>
       <c r="B46">
-        <v>-0.00047727172475474269</v>
+        <v>-0.00096968988320075974</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.12510623944258573</v>
       </c>
       <c r="B47">
-        <v>-0.00051743769488952292</v>
+        <v>-0.0010979041948686941</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.12153177545851186</v>
       </c>
       <c r="B48">
-        <v>-0.00055477775283190132</v>
+        <v>-0.0012175198350099468</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.11795731147443798</v>
       </c>
       <c r="B49">
-        <v>-0.00059365222890772379</v>
+        <v>-0.0013341478388993367</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.11438284749036409</v>
       </c>
       <c r="B50">
-        <v>-0.00063842145344283549</v>
+        <v>-0.0014533992418116796</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.11080838350629021</v>
       </c>
       <c r="B51">
-        <v>-0.0006921651990828225</v>
+        <v>-0.0015792384068672566</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.10723391952221634</v>
       </c>
       <c r="B52">
-        <v>-0.00075284100775223394</v>
+        <v>-0.001709043008568204</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.10365945553814247</v>
       </c>
       <c r="B53">
-        <v>-0.00081712586369535941</v>
+        <v>-0.0018385440492621203</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.1000849915540686</v>
       </c>
       <c r="B54">
-        <v>-0.00088169675115648929</v>
+        <v>-0.0019634725312966069</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.0965105275699947</v>
       </c>
       <c r="B55">
-        <v>-0.00094402557398804625</v>
+        <v>-0.002080581265731382</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.092936063585920825</v>
       </c>
       <c r="B56">
-        <v>-0.0010047639144749863</v>
+        <v>-0.00219071029847464</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.089361599601846947</v>
       </c>
       <c r="B57">
-        <v>-0.0010653582745103985</v>
+        <v>-0.0022957214841466968</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.085787135617773083</v>
       </c>
       <c r="B58">
-        <v>-0.0011272551559873719</v>
+        <v>-0.0023974766773678649</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.0822126716336992</v>
       </c>
       <c r="B59">
-        <v>-0.0011917270236578015</v>
+        <v>-0.0024976137424734092</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.078638207649625314</v>
       </c>
       <c r="B60">
-        <v>-0.0012593501937088031</v>
+        <v>-0.002596874582658388</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.075063743665551436</v>
       </c>
       <c r="B61">
-        <v>-0.0013305269451862984</v>
+        <v>-0.002695777110832809</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.071489279681477558</v>
       </c>
       <c r="B62">
-        <v>-0.0014056595571362094</v>
+        <v>-0.0027948392399066808</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.06791481569740368</v>
       </c>
       <c r="B63">
-        <v>-0.001484086796390092</v>
+        <v>-0.00289321127308832</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.0643403517133298</v>
       </c>
       <c r="B64">
-        <v>-0.0015608933809220431</v>
+        <v>-0.0029845730747792816</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.060765887729255931</v>
       </c>
       <c r="B65">
-        <v>-0.0016301005164917936</v>
+        <v>-0.0030612368996794288</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.057191423745182046</v>
       </c>
       <c r="B66">
-        <v>-0.0016857294088590753</v>
+        <v>-0.0031155150024886257</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.053616959761108168</v>
       </c>
       <c r="B67">
-        <v>-0.0017295275525766294</v>
+        <v>-0.0031496532472525748</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.0500424957770343</v>
       </c>
       <c r="B68">
-        <v>-0.0017941475973692366</v>
+        <v>-0.0032056319354003297</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.046468031792960413</v>
       </c>
       <c r="B69">
-        <v>-0.0019048809705402205</v>
+        <v>-0.0033159666644006296</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.042893567808886542</v>
       </c>
       <c r="B70">
-        <v>-0.0020266690545350332</v>
+        <v>-0.0034355797784975921</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.039319103824812657</v>
       </c>
       <c r="B71">
-        <v>-0.0021212881342582545</v>
+        <v>-0.0035153240021335744</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.035744639840738779</v>
       </c>
       <c r="B72">
-        <v>-0.0021982041493088466</v>
+        <v>-0.0035673668337685041</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0321701758566649</v>
       </c>
       <c r="B73">
-        <v>-0.0022732286918818192</v>
+        <v>-0.003612034229263253</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.028595711872591023</v>
       </c>
       <c r="B74">
-        <v>-0.0023398663098620014</v>
+        <v>-0.0036409712000648924</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.025021247888517149</v>
       </c>
       <c r="B75">
-        <v>-0.0023859229465628884</v>
+        <v>-0.0036384957485494553</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.021446783904443271</v>
       </c>
       <c r="B76">
-        <v>-0.0023987171713228325</v>
+        <v>-0.0035882987852226184</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.017872319920369389</v>
       </c>
       <c r="B77">
-        <v>-0.0023665080642459552</v>
+        <v>-0.0034752802092095116</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.014297855936295512</v>
       </c>
       <c r="B78">
-        <v>-0.0022818041224745987</v>
+        <v>-0.0032898029659834314</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.010723391952221635</v>
       </c>
       <c r="B79">
-        <v>-0.0021318343061694218</v>
+        <v>-0.0030154418030324836</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0071489279681477558</v>
       </c>
       <c r="B80">
-        <v>-0.0018941927814741999</v>
+        <v>-0.0026233834342252703</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0035744639840738779</v>
       </c>
       <c r="B81">
-        <v>-0.0015138542461173425</v>
+        <v>-0.0020428749157602758</v>
       </c>
     </row>
     <row r="82" spans="1:2">
